--- a/projet1_stats_descriptives_depenses_sante_ocde.xlsx.xlsx
+++ b/projet1_stats_descriptives_depenses_sante_ocde.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ctv/Documents/LeCoinStat/Mes projets /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{589C20AE-A5AD-2D48-B06E-38975DD1B309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368CFFC5-1914-1343-BEC5-0B63A69B5CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="onnées" sheetId="1" r:id="rId1"/>
@@ -19,27 +19,10 @@
     <sheet name="Overview" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">onnées!$B$8:$B$45</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">onnées!$C$7</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">onnées!$B$8:$B$45</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">onnées!$C$7</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">onnées!$B$8:$B$45</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">onnées!$C$7</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">onnées!$B$8:$B$45</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">onnées!$C$7</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">onnées!$C$8:$C$45</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">onnées!$B$8:$B$45</definedName>
-    <definedName name="_xlchart.v5.1" hidden="1">onnées!$B$7</definedName>
-    <definedName name="_xlchart.v5.2" hidden="1">onnées!$B$8:$B$45</definedName>
-    <definedName name="_xlchart.v5.3" hidden="1">onnées!$C$7</definedName>
-    <definedName name="_xlchart.v5.4" hidden="1">onnées!$C$8:$C$45</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">onnées!$B$8:$B$45</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">onnées!$C$7</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">onnées!$C$8:$C$45</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">onnées!$C$8:$C$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -870,7 +853,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#,##0.0\ _€"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0\ _€"/>
   </numFmts>
   <fonts count="98" x14ac:knownFonts="1">
     <font>
@@ -2307,118 +2290,118 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="56" fillId="58" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="58" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="78" fillId="80" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="78" fillId="80" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="36" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="34" fillId="36" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="50" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="50" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="28" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="28" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="68" fillId="70" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="68" fillId="70" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="42" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="42" fillId="44" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="52" fillId="54" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="52" fillId="54" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="64" fillId="66" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="64" fillId="66" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="48" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="48" fillId="50" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="44" fillId="46" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="44" fillId="46" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="72" fillId="74" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="72" fillId="74" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="22" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="66" fillId="68" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="66" fillId="68" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="70" fillId="72" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="70" fillId="72" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="46" fillId="48" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="48" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="60" fillId="62" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="60" fillId="62" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="28" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="30" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="38" fillId="40" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="40" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="80" fillId="82" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="80" fillId="82" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="16" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="30" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="30" fillId="32" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="24" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="74" fillId="76" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="74" fillId="76" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="40" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="40" fillId="42" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="54" fillId="56" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="54" fillId="56" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="58" fillId="60" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="58" fillId="60" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="62" fillId="64" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="62" fillId="64" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="32" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="32" fillId="34" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="76" fillId="78" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="76" fillId="78" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="168" fontId="82" fillId="84" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="82" fillId="84" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2439,29 +2422,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2479,7 +2439,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="#,##0.0\ _€"/>
+      <numFmt numFmtId="164" formatCode="#,##0.0\ _€"/>
       <fill>
         <patternFill patternType="none">
           <fgColor auto="1"/>
@@ -2571,6 +2531,29 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2585,226 +2568,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:axId val="525612607"/>
-        <c:axId val="525614399"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="525612607"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="525614399"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="525614399"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="525612607"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -3412,7 +3175,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.11</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3525,10 +3288,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.18</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.20</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3585,7 +3348,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{9FD36DE8-8B8E-A14D-B160-BF1548A2ADDB}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.19</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>Dépenses de santé par habitants</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3800,48 +3563,8 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3852,7 +3575,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -3865,7 +3588,7 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
@@ -3882,7 +3605,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -3898,7 +3621,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -3942,35 +3665,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -3982,30 +3705,31 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -4107,14 +3831,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -4204,20 +3922,20 @@
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -4230,6 +3948,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -4261,7 +3990,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -4270,14 +3999,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -4331,521 +4059,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="373">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5360,7 +4580,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="371">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5838,47 +5058,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Graphique 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D448751-7AF3-CEF1-61FA-8FCC7E4436EB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5965,8 +5144,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10015369" y="5737423"/>
-              <a:ext cx="6021939" cy="3890434"/>
+              <a:off x="9964569" y="5864423"/>
+              <a:ext cx="5992306" cy="3979334"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6043,8 +5222,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9727271" y="1419888"/>
-              <a:ext cx="7539334" cy="3812512"/>
+              <a:off x="9680704" y="1449521"/>
+              <a:ext cx="7501234" cy="3901412"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6078,24 +5257,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{74AC4960-4BB3-7141-A7CF-B6D97023225A}" name="Tableau3" displayName="Tableau3" ref="B7:C45" totalsRowShown="0" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{74AC4960-4BB3-7141-A7CF-B6D97023225A}" name="Tableau3" displayName="Tableau3" ref="B7:C45" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="B7:C45" xr:uid="{74AC4960-4BB3-7141-A7CF-B6D97023225A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:C45">
     <sortCondition ref="B7:B45"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{61597AEC-793B-9F4B-9E3A-935E069D99E6}" name="Pays" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{8AFB5C3C-8C8F-6D40-B306-320EF120D5D5}" name="Dépenses de santé par habitants" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{61597AEC-793B-9F4B-9E3A-935E069D99E6}" name="Pays" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{8AFB5C3C-8C8F-6D40-B306-320EF120D5D5}" name="Dépenses de santé par habitants" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52F64984-3C32-F84A-A9BF-2BCBA46BCBEF}" name="Tableau1" displayName="Tableau1" ref="C4:D21" headerRowCount="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{52F64984-3C32-F84A-A9BF-2BCBA46BCBEF}" name="Tableau1" displayName="Tableau1" ref="C4:D21" headerRowCount="0" headerRowDxfId="11">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E446466C-6CA2-CC44-A7BB-F683B450A5D8}" name="Colonne1" totalsRowLabel="Total" headerRowDxfId="2" dataDxfId="6" totalsRowDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{CDE5BAB6-AC6D-744C-ABF0-91C09F0DAD7D}" name="Colonne2" totalsRowFunction="sum" headerRowDxfId="3" dataDxfId="5" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{E446466C-6CA2-CC44-A7BB-F683B450A5D8}" name="Colonne1" totalsRowLabel="Total" headerRowDxfId="10" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{CDE5BAB6-AC6D-744C-ABF0-91C09F0DAD7D}" name="Colonne2" totalsRowFunction="sum" headerRowDxfId="7" dataDxfId="6" totalsRowDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6983,9 +6162,8 @@
     <mergeCell ref="C24:C27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/projet1_stats_descriptives_depenses_sante_ocde.xlsx.xlsx
+++ b/projet1_stats_descriptives_depenses_sante_ocde.xlsx.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
+  <fileSharing readOnlyRecommended="1" userName="Ctv" algorithmName="SHA-512" hashValue="aFuLlEj28sMnGnk1aJCjPxVcs9y5NPd4iNHsrCSUdeulharEwD1Mv4QFvhkHP5qC0qr3qRhAJw4vbpqnBkHbiA==" saltValue="frqM2x5Ixgm7ukOODUwZzg==" spinCount="100000"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ctv/Documents/LeCoinStat/Mes projets /"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ctv/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368CFFC5-1914-1343-BEC5-0B63A69B5CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF88B3B-3A1C-3949-9ABD-C9EE4BCE7A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="onnées" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,6 @@
     <definedName name="_xlchart.v1.3" hidden="1">onnées!$C$8:$C$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
